--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF07BF1-B21A-4283-9CDE-7D0320EDD876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8285E013-BAAE-483E-9E43-C1A75CB1BBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1968" yWindow="312" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
-    <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその2" sheetId="3" r:id="rId2"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC (2)" sheetId="4" r:id="rId2"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC (3)" sheetId="5" r:id="rId3"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその4" sheetId="3" r:id="rId4"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="24">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -76,6 +78,53 @@
   </si>
   <si>
     <t>見積もり</t>
+  </si>
+  <si>
+    <t>語彙</t>
+    <rPh sb="0" eb="2">
+      <t>ゴイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOEIC Part2-2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択肢</t>
+    <rPh sb="0" eb="3">
+      <t>センタクシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOEIC Part2-3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOEIC Part2-4</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1340,764 +1389,872 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82227981-1382-4A89-8594-A315650E478D}">
-  <dimension ref="A1:E103"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBB48852-4D76-4DC4-9F44-5ABB7685BDF4}">
+  <dimension ref="A1:F103"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="5.5" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="44.8984375" customWidth="1"/>
+    <col min="3" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1">
+    <row r="1" spans="1:6" s="2" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
       <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
       <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
       <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
       <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
       <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
       <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
       <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
       <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
       <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
       <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
       <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
       <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>26</v>
       </c>
-      <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>29</v>
       </c>
-      <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="4"/>
+      <c r="F33" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>33</v>
       </c>
-      <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>34</v>
       </c>
-      <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>36</v>
       </c>
-      <c r="D38" s="4"/>
       <c r="E38" s="4"/>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>37</v>
       </c>
-      <c r="D39" s="4"/>
       <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>38</v>
       </c>
-      <c r="D40" s="4"/>
       <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>39</v>
       </c>
-      <c r="D41" s="4"/>
       <c r="E41" s="4"/>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>40</v>
       </c>
-      <c r="D42" s="4"/>
       <c r="E42" s="4"/>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="D43" s="4"/>
       <c r="E43" s="4"/>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>42</v>
       </c>
-      <c r="D44" s="4"/>
       <c r="E44" s="4"/>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>43</v>
       </c>
-      <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>44</v>
       </c>
-      <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>45</v>
       </c>
-      <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>46</v>
       </c>
-      <c r="D48" s="4"/>
       <c r="E48" s="4"/>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>47</v>
       </c>
-      <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>48</v>
       </c>
-      <c r="D50" s="4"/>
       <c r="E50" s="4"/>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="D51" s="4"/>
       <c r="E51" s="4"/>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>50</v>
       </c>
-      <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>51</v>
       </c>
-      <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>52</v>
       </c>
-      <c r="D54" s="4"/>
       <c r="E54" s="4"/>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>53</v>
       </c>
-      <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="D56" s="4"/>
       <c r="E56" s="4"/>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>55</v>
       </c>
-      <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>56</v>
       </c>
-      <c r="D58" s="4"/>
       <c r="E58" s="4"/>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>57</v>
       </c>
-      <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>58</v>
       </c>
-      <c r="D60" s="4"/>
       <c r="E60" s="4"/>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="D61" s="4"/>
       <c r="E61" s="4"/>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62">
         <v>60</v>
       </c>
-      <c r="D62" s="4"/>
       <c r="E62" s="4"/>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63">
         <v>61</v>
       </c>
-      <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64">
         <v>62</v>
       </c>
-      <c r="D64" s="4"/>
       <c r="E64" s="4"/>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65">
         <v>63</v>
       </c>
-      <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66">
         <v>64</v>
       </c>
-      <c r="D66" s="4"/>
       <c r="E66" s="4"/>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67">
         <v>65</v>
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68">
         <v>66</v>
       </c>
-      <c r="D68" s="4"/>
       <c r="E68" s="4"/>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69">
         <v>67</v>
       </c>
-      <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70">
         <v>68</v>
       </c>
-      <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71">
         <v>69</v>
       </c>
-      <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72">
         <v>70</v>
       </c>
-      <c r="D72" s="4"/>
       <c r="E72" s="4"/>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73">
         <v>71</v>
       </c>
-      <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74">
         <v>72</v>
       </c>
-      <c r="D74" s="4"/>
       <c r="E74" s="4"/>
-    </row>
-    <row r="75" spans="1:5">
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75">
         <v>73</v>
       </c>
-      <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-    </row>
-    <row r="76" spans="1:5">
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76">
         <v>74</v>
       </c>
-      <c r="D76" s="4"/>
       <c r="E76" s="4"/>
-    </row>
-    <row r="77" spans="1:5">
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77">
         <v>75</v>
       </c>
-      <c r="D77" s="4"/>
       <c r="E77" s="4"/>
-    </row>
-    <row r="78" spans="1:5">
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78">
         <v>76</v>
       </c>
-      <c r="D78" s="4"/>
       <c r="E78" s="4"/>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79">
         <v>77</v>
       </c>
-      <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80">
         <v>78</v>
       </c>
-      <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-    </row>
-    <row r="81" spans="1:5">
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81">
         <v>79</v>
       </c>
-      <c r="D81" s="4"/>
       <c r="E81" s="4"/>
-    </row>
-    <row r="82" spans="1:5">
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82">
         <v>80</v>
       </c>
-      <c r="D82" s="4"/>
       <c r="E82" s="4"/>
-    </row>
-    <row r="83" spans="1:5">
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83">
         <v>81</v>
       </c>
-      <c r="D83" s="4"/>
       <c r="E83" s="4"/>
-    </row>
-    <row r="84" spans="1:5">
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84">
         <v>82</v>
       </c>
-      <c r="D84" s="4"/>
       <c r="E84" s="4"/>
-    </row>
-    <row r="85" spans="1:5">
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85">
         <v>83</v>
       </c>
-      <c r="D85" s="4"/>
       <c r="E85" s="4"/>
-    </row>
-    <row r="86" spans="1:5">
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86">
         <v>84</v>
       </c>
-      <c r="D86" s="4"/>
       <c r="E86" s="4"/>
-    </row>
-    <row r="87" spans="1:5">
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87">
         <v>85</v>
       </c>
-      <c r="D87" s="4"/>
       <c r="E87" s="4"/>
-    </row>
-    <row r="88" spans="1:5">
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88">
         <v>86</v>
       </c>
-      <c r="D88" s="4"/>
       <c r="E88" s="4"/>
-    </row>
-    <row r="89" spans="1:5">
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89">
         <v>87</v>
       </c>
-      <c r="D89" s="4"/>
       <c r="E89" s="4"/>
-    </row>
-    <row r="90" spans="1:5">
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90">
         <v>88</v>
       </c>
-      <c r="D90" s="4"/>
       <c r="E90" s="4"/>
-    </row>
-    <row r="91" spans="1:5">
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91">
         <v>89</v>
       </c>
-      <c r="D91" s="4"/>
       <c r="E91" s="4"/>
-    </row>
-    <row r="92" spans="1:5">
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92">
         <v>90</v>
       </c>
-      <c r="D92" s="4"/>
       <c r="E92" s="4"/>
-    </row>
-    <row r="93" spans="1:5">
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93">
         <v>91</v>
       </c>
-      <c r="D93" s="4"/>
       <c r="E93" s="4"/>
-    </row>
-    <row r="94" spans="1:5">
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94">
         <v>92</v>
       </c>
-      <c r="D94" s="4"/>
       <c r="E94" s="4"/>
-    </row>
-    <row r="95" spans="1:5">
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95">
         <v>93</v>
       </c>
-      <c r="D95" s="4"/>
       <c r="E95" s="4"/>
-    </row>
-    <row r="96" spans="1:5">
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96">
         <v>94</v>
       </c>
-      <c r="D96" s="4"/>
       <c r="E96" s="4"/>
-    </row>
-    <row r="97" spans="1:5">
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97">
         <v>95</v>
       </c>
-      <c r="D97" s="4"/>
       <c r="E97" s="4"/>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98">
         <v>96</v>
       </c>
-      <c r="D98" s="4"/>
       <c r="E98" s="4"/>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99">
         <v>97</v>
       </c>
-      <c r="D99" s="4"/>
       <c r="E99" s="4"/>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100">
         <v>98</v>
       </c>
-      <c r="D100" s="4"/>
       <c r="E100" s="4"/>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101">
         <v>99</v>
       </c>
-      <c r="D101" s="4"/>
       <c r="E101" s="4"/>
-    </row>
-    <row r="102" spans="1:5">
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102">
         <v>100</v>
       </c>
-      <c r="D102" s="4"/>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="D103" s="4"/>
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="E103" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5D4C5161-CE35-446F-BE72-877F8A629A69}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1E9532C8-1BCF-4580-BAE2-76DF5394C002}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D102</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{99B777D4-2FD5-4499-9BA6-A4A3C5DD5E2D}">
           <x14:formula1>
             <xm:f>list!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D103 E3:E101</xm:sqref>
+          <xm:sqref>E3:E103 F3:F101</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2106,18 +2263,1731 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5046F435-14CC-4C46-8E6A-CB119F2562F3}">
+  <dimension ref="A1:F103"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="2" width="5.5" customWidth="1"/>
+    <col min="3" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="E18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="E103" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0EDE332E-F392-40E1-ABF7-BBA87A3CB11A}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D102</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{45253533-4024-40C6-A5B8-259210133F2C}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E103 F3:F101</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82227981-1382-4A89-8594-A315650E478D}">
+  <dimension ref="A1:F103"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="2" width="5.5" customWidth="1"/>
+    <col min="3" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="E103" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5D4C5161-CE35-446F-BE72-877F8A629A69}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E103 F3:F101</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{91138615-7564-4337-824C-7EABC715B6E6}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D102</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,16 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8285E013-BAAE-483E-9E43-C1A75CB1BBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0342A3BA-09B5-422E-85ED-8C14D913F21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1968" yWindow="312" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC (2)" sheetId="4" r:id="rId2"/>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC (3)" sheetId="5" r:id="rId3"/>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその4" sheetId="3" r:id="rId4"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId5"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC5" sheetId="6" r:id="rId5"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC6" sheetId="7" r:id="rId6"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC8" sheetId="9" r:id="rId7"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC 7" sheetId="8" r:id="rId8"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="27">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -126,12 +130,24 @@
     <t>TOEIC Part2-4</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>tournament</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hoarse</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>herd</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +183,13 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -194,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -208,6 +231,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1499,6 +1526,9 @@
       <c r="A9">
         <v>7</v>
       </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
@@ -2267,7 +2297,8 @@
   <dimension ref="A1:F103"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="2" width="5.5" customWidth="1"/>
+    <col min="1" max="1" width="5.5" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" customWidth="1"/>
     <col min="3" max="4" width="7" customWidth="1"/>
     <col min="5" max="5" width="8.3984375" customWidth="1"/>
   </cols>
@@ -2368,7 +2399,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -2450,13 +2481,17 @@
       <c r="E17" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C18" s="3"/>
       <c r="E18" s="4" t="s">
         <v>3</v>
@@ -3170,7 +3205,9 @@
       <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
@@ -3375,7 +3412,9 @@
       <c r="E24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
@@ -3390,6 +3429,9 @@
     <row r="26" spans="1:6">
       <c r="A26">
         <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
       </c>
       <c r="D26" t="s">
         <v>20</v>
@@ -3965,6 +4007,3445 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3309985-673E-45A0-ACE8-B24993B75774}">
+  <dimension ref="A1:F103"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="2" width="5.5" customWidth="1"/>
+    <col min="3" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="E103" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AEB9BD2E-CADA-480F-9134-19B2FD2D034E}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D102</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0E74F1AF-B7B8-40D1-940F-FEF087BDBE98}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E103 F3:F101</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB7CD3-2AFD-42A8-81B4-393AE03E5F6C}">
+  <dimension ref="A1:F103"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="2" width="5.5" customWidth="1"/>
+    <col min="3" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="E103" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2A8BFCB5-24D0-4330-BDB7-7248D43EE354}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E103 F3:F101</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DE60A544-61D7-4618-937A-A78319AC1C35}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D102</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0631C6D6-81A8-4D66-BCC0-696B1EF7F0FD}">
+  <dimension ref="A1:F103"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="2" width="5.5" customWidth="1"/>
+    <col min="3" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="E103" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0A7D13FC-EFFE-47B8-B4B2-F7096271A03F}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E103 F3:F101</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{002C89E1-4437-4F45-B7EA-D6DCF1C60809}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D102</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB508468-0288-4183-AE66-E7A51E93BBA3}">
+  <dimension ref="A1:F103"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="2" width="5.5" customWidth="1"/>
+    <col min="3" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="E103" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1EAE938F-5ED4-40C3-83D9-ADF5864C561A}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D102</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C13207DA-0BF0-4CF8-87B3-F8C424032D1C}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E103 F3:F101</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0342A3BA-09B5-422E-85ED-8C14D913F21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8166C5-D955-42EB-AA09-1ADA0D5AE7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその4" sheetId="3" r:id="rId4"/>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC5" sheetId="6" r:id="rId5"/>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC6" sheetId="7" r:id="rId6"/>
-    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC8" sheetId="9" r:id="rId7"/>
-    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC 7" sheetId="8" r:id="rId8"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC 7" sheetId="8" r:id="rId7"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC8" sheetId="9" r:id="rId8"/>
     <sheet name="list" sheetId="2" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="40">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -141,6 +141,55 @@
   <si>
     <t>herd</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>minutes</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>weight the costs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>reach a consensus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>given the time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>billboard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>demographic</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>metrics</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>impressions</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>議事録</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>掲示板</t>
+  </si>
+  <si>
+    <t>人口統計</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指標</t>
+  </si>
+  <si>
+    <t>印象</t>
   </si>
 </sst>
 </file>
@@ -4011,7 +4060,8 @@
   <dimension ref="A1:F103"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="2" width="5.5" customWidth="1"/>
+    <col min="1" max="1" width="5.5" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" customWidth="1"/>
     <col min="3" max="4" width="7" customWidth="1"/>
     <col min="5" max="5" width="8.3984375" customWidth="1"/>
   </cols>
@@ -4150,7 +4200,9 @@
       <c r="E11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
@@ -4168,6 +4220,12 @@
       <c r="A13">
         <v>11</v>
       </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
@@ -4186,7 +4244,9 @@
       <c r="E14" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
@@ -4204,6 +4264,9 @@
       <c r="A16">
         <v>14</v>
       </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
       <c r="D16" t="s">
         <v>16</v>
       </c>
@@ -4222,7 +4285,9 @@
       <c r="E17" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
@@ -4316,6 +4381,9 @@
       <c r="A25">
         <v>23</v>
       </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
       <c r="D25" t="s">
         <v>16</v>
       </c>
@@ -4340,11 +4408,14 @@
       <c r="A27">
         <v>25</v>
       </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
       <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" s="4"/>
     </row>
@@ -5037,7 +5108,9 @@
       <c r="E10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
@@ -5061,7 +5134,9 @@
       <c r="E12" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
@@ -5076,7 +5151,7 @@
       <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14">
+      <c r="A14" s="7">
         <v>12</v>
       </c>
       <c r="D14" t="s">
@@ -5132,7 +5207,9 @@
       <c r="D18" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6">
@@ -5142,14 +5219,21 @@
       <c r="D19" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="E20" s="4"/>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6">
@@ -5158,42 +5242,72 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="E21" s="4"/>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="E25" s="4"/>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="E26" s="4"/>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6">
@@ -5201,7 +5315,7 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>5</v>
@@ -5212,7 +5326,12 @@
       <c r="A28">
         <v>26</v>
       </c>
-      <c r="E28" s="4"/>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6">
@@ -5751,7 +5870,7 @@
           <x14:formula1>
             <xm:f>list!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E103 F3:F101</xm:sqref>
+          <xm:sqref>F3:F101 E3:E103</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DE60A544-61D7-4618-937A-A78319AC1C35}">
           <x14:formula1>
@@ -5766,6 +5885,880 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB508468-0288-4183-AE66-E7A51E93BBA3}">
+  <dimension ref="A1:F103"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="5.5" customWidth="1"/>
+    <col min="2" max="2" width="19.59765625" customWidth="1"/>
+    <col min="3" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="E103" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1EAE938F-5ED4-40C3-83D9-ADF5864C561A}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D102</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C13207DA-0BF0-4CF8-87B3-F8C424032D1C}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E103 F3:F101</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0631C6D6-81A8-4D66-BCC0-696B1EF7F0FD}">
   <dimension ref="A1:F103"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -5806,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -5828,7 +6821,7 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -5847,6 +6840,9 @@
       <c r="A7">
         <v>5</v>
       </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
@@ -5855,7 +6851,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -5864,8 +6860,8 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="D9" t="s">
-        <v>20</v>
+      <c r="D9" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -5874,8 +6870,8 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>16</v>
+      <c r="D10" t="s">
+        <v>20</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="4"/>
@@ -5895,7 +6891,7 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -5905,7 +6901,7 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -5915,7 +6911,7 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -5925,7 +6921,7 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -5935,7 +6931,7 @@
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -5945,7 +6941,7 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -5957,7 +6953,7 @@
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -5977,19 +6973,19 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21">
+      <c r="A21" s="7">
         <v>19</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -5998,6 +6994,9 @@
       <c r="A22">
         <v>20</v>
       </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
@@ -6005,6 +7004,9 @@
       <c r="A23">
         <v>21</v>
       </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
@@ -6013,14 +7015,17 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25">
+      <c r="A25" s="7">
         <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -6030,7 +7035,7 @@
         <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -6040,7 +7045,7 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -6602,849 +7607,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB508468-0288-4183-AE66-E7A51E93BBA3}">
-  <dimension ref="A1:F103"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <cols>
-    <col min="1" max="2" width="5.5" customWidth="1"/>
-    <col min="3" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="8.3984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="D24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="D26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>42</v>
-      </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>43</v>
-      </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>44</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>45</v>
-      </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>46</v>
-      </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>47</v>
-      </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>48</v>
-      </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>49</v>
-      </c>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>50</v>
-      </c>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>51</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>53</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>55</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>56</v>
-      </c>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>57</v>
-      </c>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>58</v>
-      </c>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>59</v>
-      </c>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>60</v>
-      </c>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>61</v>
-      </c>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>62</v>
-      </c>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>63</v>
-      </c>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>64</v>
-      </c>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>65</v>
-      </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>66</v>
-      </c>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>67</v>
-      </c>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>68</v>
-      </c>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>69</v>
-      </c>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>70</v>
-      </c>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>71</v>
-      </c>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>72</v>
-      </c>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>73</v>
-      </c>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>74</v>
-      </c>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>75</v>
-      </c>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>76</v>
-      </c>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>77</v>
-      </c>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>78</v>
-      </c>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>79</v>
-      </c>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>80</v>
-      </c>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>81</v>
-      </c>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>82</v>
-      </c>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>83</v>
-      </c>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>84</v>
-      </c>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>85</v>
-      </c>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>86</v>
-      </c>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>87</v>
-      </c>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>88</v>
-      </c>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>89</v>
-      </c>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>90</v>
-      </c>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>91</v>
-      </c>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>92</v>
-      </c>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>93</v>
-      </c>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>94</v>
-      </c>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>95</v>
-      </c>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>96</v>
-      </c>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>97</v>
-      </c>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>98</v>
-      </c>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>99</v>
-      </c>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>100</v>
-      </c>
-      <c r="E102" s="4"/>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="E103" s="4"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1EAE938F-5ED4-40C3-83D9-ADF5864C561A}">
-          <x14:formula1>
-            <xm:f>list!$B$1:$B$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>D3:D102</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C13207DA-0BF0-4CF8-87B3-F8C424032D1C}">
-          <x14:formula1>
-            <xm:f>list!$A$1:$A$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>E3:E103 F3:F101</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B3"/>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8166C5-D955-42EB-AA09-1ADA0D5AE7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0E46F8-1499-4AFA-9A49-ED57C5D02E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,8 @@
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC6" sheetId="7" r:id="rId6"/>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC 7" sheetId="8" r:id="rId7"/>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC8" sheetId="9" r:id="rId8"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId9"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEIC9" sheetId="10" r:id="rId9"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="40">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -196,7 +197,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,6 +240,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -266,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -284,6 +297,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1464,6 +1479,38 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBB48852-4D76-4DC4-9F44-5ABB7685BDF4}">
   <dimension ref="A1:F103"/>
@@ -7608,33 +7655,1073 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
-  <dimension ref="A1:B3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{213E29A3-2BCB-445B-809C-D00910847B1C}">
+  <dimension ref="A1:F103"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="5.5" style="9" customWidth="1"/>
+    <col min="2" max="2" width="5.5" customWidth="1"/>
+    <col min="3" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>7</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="B3" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9">
         <v>21</v>
       </c>
+      <c r="D23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="9">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="9">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="9">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="9">
+        <v>26</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="9">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="9">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="9">
+        <v>29</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="9">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="9">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="9">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="9">
+        <v>33</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="9">
+        <v>34</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="9">
+        <v>35</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="9">
+        <v>36</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="9">
+        <v>37</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="9">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="9">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="9">
+        <v>40</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="9">
+        <v>41</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="9">
+        <v>42</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="9">
+        <v>43</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="9">
+        <v>44</v>
+      </c>
+      <c r="D46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="9">
+        <v>45</v>
+      </c>
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="9">
+        <v>46</v>
+      </c>
+      <c r="D48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="9">
+        <v>47</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="9">
+        <v>48</v>
+      </c>
+      <c r="D50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="9">
+        <v>49</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="9">
+        <v>50</v>
+      </c>
+      <c r="D52" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="9">
+        <v>51</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="9">
+        <v>52</v>
+      </c>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="9">
+        <v>53</v>
+      </c>
+      <c r="D55" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="9">
+        <v>54</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="9">
+        <v>55</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="9">
+        <v>56</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="9">
+        <v>57</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="9">
+        <v>58</v>
+      </c>
+      <c r="D60" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="9">
+        <v>59</v>
+      </c>
+      <c r="D61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="9">
+        <v>60</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="9">
+        <v>61</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="9">
+        <v>62</v>
+      </c>
+      <c r="D64" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="9">
+        <v>63</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="9">
+        <v>64</v>
+      </c>
+      <c r="D66" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="9">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="9">
+        <v>66</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="9">
+        <v>67</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="9">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="9">
+        <v>69</v>
+      </c>
+      <c r="D71" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="9">
+        <v>70</v>
+      </c>
+      <c r="D72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="9">
+        <v>71</v>
+      </c>
+      <c r="D73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="9">
+        <v>72</v>
+      </c>
+      <c r="D74" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="9">
+        <v>73</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="9">
+        <v>74</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="9">
+        <v>75</v>
+      </c>
+      <c r="D77" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="9">
+        <v>76</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="9">
+        <v>77</v>
+      </c>
+      <c r="D79" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="9">
+        <v>78</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="9">
+        <v>79</v>
+      </c>
+      <c r="D81" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="9">
+        <v>80</v>
+      </c>
+      <c r="D82" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="9">
+        <v>81</v>
+      </c>
+      <c r="D83" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="9">
+        <v>82</v>
+      </c>
+      <c r="D84" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="9">
+        <v>83</v>
+      </c>
+      <c r="D85" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="9">
+        <v>84</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="9">
+        <v>85</v>
+      </c>
+      <c r="D87" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="9">
+        <v>86</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="9">
+        <v>87</v>
+      </c>
+      <c r="D89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="9">
+        <v>88</v>
+      </c>
+      <c r="D90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="9">
+        <v>89</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="9">
+        <v>90</v>
+      </c>
+      <c r="D92" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="9">
+        <v>91</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="9">
+        <v>92</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="9">
+        <v>93</v>
+      </c>
+      <c r="D95" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="9">
+        <v>94</v>
+      </c>
+      <c r="D96" s="7"/>
+      <c r="E96" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="9">
+        <v>95</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="9">
+        <v>96</v>
+      </c>
+      <c r="D98" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="9">
+        <v>97</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="9">
+        <v>98</v>
+      </c>
+      <c r="D100" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="9">
+        <v>99</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="9">
+        <v>100</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="E103" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2663CC7A-031A-40CB-9468-52EDB3374021}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D102</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{270AE48D-0B0D-4221-98E0-C92E0F96236B}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E103 F3:F101</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0E46F8-1499-4AFA-9A49-ED57C5D02E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410DF92A-0462-4F67-ABFD-9F3A6865E4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,8 @@
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC 7" sheetId="8" r:id="rId7"/>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC8" sheetId="9" r:id="rId8"/>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC9" sheetId="10" r:id="rId9"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId10"/>
+    <sheet name="toeic10" sheetId="11" r:id="rId10"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="48">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -191,6 +192,36 @@
   </si>
   <si>
     <t>印象</t>
+  </si>
+  <si>
+    <t>auditorium</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>trunk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>courier</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>clauses</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>講堂</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>樹幹</t>
+  </si>
+  <si>
+    <t>宅配便</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>条項</t>
   </si>
 </sst>
 </file>
@@ -1480,6 +1511,255 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B83E43-6935-43F1-8B4E-4A9CC4B8F691}">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="9"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DBD795AA-7844-4710-8706-4580983EBC49}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F25</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7A845402-9DA7-4D78-8333-A3C13C3D382C}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D25</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -7660,7 +7940,7 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.5" style="9" customWidth="1"/>
-    <col min="2" max="2" width="5.5" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="4" width="7" customWidth="1"/>
     <col min="5" max="5" width="8.3984375" customWidth="1"/>
   </cols>
@@ -8205,10 +8485,15 @@
       <c r="A53" s="9">
         <v>51</v>
       </c>
+      <c r="D53" t="s">
+        <v>16</v>
+      </c>
       <c r="E53" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F53" s="4"/>
+      <c r="F53" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="9">
@@ -8234,10 +8519,15 @@
       <c r="A56" s="9">
         <v>54</v>
       </c>
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
       <c r="E56" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F56" s="4"/>
+      <c r="F56" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="9">
@@ -8485,6 +8775,12 @@
       <c r="A81" s="9">
         <v>79</v>
       </c>
+      <c r="B81" t="s">
+        <v>40</v>
+      </c>
+      <c r="C81" t="s">
+        <v>44</v>
+      </c>
       <c r="D81" t="s">
         <v>18</v>
       </c>
@@ -8545,6 +8841,12 @@
       <c r="A87" s="9">
         <v>85</v>
       </c>
+      <c r="B87" t="s">
+        <v>41</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="D87" t="s">
         <v>18</v>
       </c>
@@ -8555,6 +8857,12 @@
       <c r="A88" s="9">
         <v>86</v>
       </c>
+      <c r="B88" t="s">
+        <v>42</v>
+      </c>
+      <c r="C88" t="s">
+        <v>46</v>
+      </c>
       <c r="D88" s="7" t="s">
         <v>18</v>
       </c>
@@ -8605,10 +8913,15 @@
       <c r="A93" s="9">
         <v>91</v>
       </c>
+      <c r="D93" t="s">
+        <v>20</v>
+      </c>
       <c r="E93" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F93" s="4"/>
+      <c r="F93" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="9">
@@ -8683,6 +8996,12 @@
     <row r="101" spans="1:6">
       <c r="A101" s="9">
         <v>99</v>
+      </c>
+      <c r="B101" t="s">
+        <v>43</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>20</v>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410DF92A-0462-4F67-ABFD-9F3A6865E4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D99ECD-A679-4CEE-AAA6-1D14BBE485D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="56">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -222,6 +222,42 @@
   </si>
   <si>
     <t>条項</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pitch
+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>due</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>draw  from</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>equity</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>capital</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bridge
+provisional
+stopgap</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>crowdfuing
+enticing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>depleting</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1543,9 +1579,12 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="36">
       <c r="A3" s="9">
         <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
@@ -1569,6 +1608,9 @@
       <c r="A5" s="9">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
@@ -1578,6 +1620,9 @@
     <row r="6" spans="1:6">
       <c r="A6" s="9">
         <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
@@ -1589,6 +1634,9 @@
       <c r="A7" s="9">
         <v>6</v>
       </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
       <c r="D7" t="s">
         <v>18</v>
       </c>
@@ -1599,6 +1647,9 @@
       <c r="A8" s="9">
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
       <c r="D8" s="9" t="s">
         <v>18</v>
       </c>
@@ -1615,19 +1666,25 @@
       <c r="E9" s="8"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="72">
       <c r="A10" s="9">
         <v>9</v>
       </c>
+      <c r="B10" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="D10" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="54">
       <c r="A11" s="9">
         <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1668,6 +1725,9 @@
     <row r="15" spans="1:6">
       <c r="A15" s="9">
         <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D99ECD-A679-4CEE-AAA6-1D14BBE485D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC39D7C-0A38-49C0-9B7D-BCE495303BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,8 @@
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC8" sheetId="9" r:id="rId8"/>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC9" sheetId="10" r:id="rId9"/>
     <sheet name="toeic10" sheetId="11" r:id="rId10"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId11"/>
+    <sheet name="toeic11" sheetId="12" r:id="rId11"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="58">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -257,6 +258,17 @@
   </si>
   <si>
     <t>depleting</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">audit </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>監査</t>
+    <rPh sb="0" eb="2">
+      <t>カンサ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1820,6 +1832,25 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E151D435-5A49-4FA2-BE5A-B44A565A5E25}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC39D7C-0A38-49C0-9B7D-BCE495303BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E147964-D0D4-41D2-83BE-17054DC588BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="9768" windowHeight="12336" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,9 @@
     <sheet name="1やり直し英語Eigo Chat Lab! TOEIC9" sheetId="10" r:id="rId9"/>
     <sheet name="toeic10" sheetId="11" r:id="rId10"/>
     <sheet name="toeic11" sheetId="12" r:id="rId11"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId12"/>
+    <sheet name="toeic12" sheetId="13" r:id="rId12"/>
+    <sheet name="toeic13" sheetId="14" r:id="rId13"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="87">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -246,12 +248,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>bridge
-provisional
-stopgap</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>crowdfuing
 enticing</t>
     <phoneticPr fontId="1"/>
@@ -271,12 +267,127 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>売り込む</t>
+  </si>
+  <si>
+    <t>二つ</t>
+  </si>
+  <si>
+    <t>資本</t>
+  </si>
+  <si>
+    <t>資本金</t>
+  </si>
+  <si>
+    <t>橋
+暫定的
+つなぎの言葉</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bridge
+provision
+stopgap</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウドフューイング
+魅力的</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>枯渇</t>
+  </si>
+  <si>
+    <t>initiative</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fiscal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>accommodate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>is  advised to do</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>breach</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>volume of  calls</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>intellectual property right law</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>audit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主導</t>
+  </si>
+  <si>
+    <t>税金</t>
+  </si>
+  <si>
+    <t>対応</t>
+  </si>
+  <si>
+    <t>推奨されています</t>
+  </si>
+  <si>
+    <t>違反</t>
+  </si>
+  <si>
+    <t>知的財産権法</t>
+  </si>
+  <si>
+    <t>監査</t>
+  </si>
+  <si>
+    <t>大量</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>footage</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hardwood,
+throughout</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>landlord</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>amenities</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>condo,
+marble</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>well-lit</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +442,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Meiryo"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -358,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -378,6 +496,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1598,6 +1717,9 @@
       <c r="B3" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
@@ -1623,6 +1745,9 @@
       <c r="B5" t="s">
         <v>49</v>
       </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
@@ -1649,6 +1774,9 @@
       <c r="B7" t="s">
         <v>51</v>
       </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
       <c r="D7" t="s">
         <v>18</v>
       </c>
@@ -1662,6 +1790,9 @@
       <c r="B8" t="s">
         <v>52</v>
       </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
       <c r="D8" s="9" t="s">
         <v>18</v>
       </c>
@@ -1683,7 +1814,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>53</v>
+        <v>62</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1691,12 +1825,15 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" ht="54">
+    <row r="11" spans="1:6" ht="72">
       <c r="A11" s="9">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -1739,7 +1876,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
@@ -1838,10 +1978,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
         <v>56</v>
-      </c>
-      <c r="B1" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1851,6 +1991,392 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{042C5E14-F060-4444-9B70-4B4B15B54946}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="19.2">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="19.2">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3136C0-79D1-407A-AFA2-2C71B9280C59}">
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="17.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="40.200000000000003" customHeight="1">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" ht="36">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AE6AC811-F8EA-4679-91E2-00A4D45E97CC}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D26</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CFB2C4DA-6C82-4DC3-ABE3-4D28506F4BFA}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F20 E21:E23</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E147964-D0D4-41D2-83BE-17054DC588BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64DF754-7974-46D1-A101-C1561FC3B2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="9768" windowHeight="12336" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,8 @@
     <sheet name="toeic11" sheetId="12" r:id="rId11"/>
     <sheet name="toeic12" sheetId="13" r:id="rId12"/>
     <sheet name="toeic13" sheetId="14" r:id="rId13"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId14"/>
+    <sheet name="toeic14" sheetId="15" r:id="rId14"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId15"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="93">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -380,6 +381,30 @@
   </si>
   <si>
     <t>well-lit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平方フィート</t>
+  </si>
+  <si>
+    <t>木のフローリング，
+全体に</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家主</t>
+  </si>
+  <si>
+    <t>設備</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分譲マンション，
+大理石</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明るい</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2128,9 +2153,10 @@
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6">
@@ -2150,6 +2176,9 @@
       <c r="B7" t="s">
         <v>81</v>
       </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
       <c r="D7" t="s">
         <v>18</v>
       </c>
@@ -2193,8 +2222,11 @@
       <c r="B11" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="C11" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -2206,6 +2238,9 @@
       <c r="B12" t="s">
         <v>83</v>
       </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
@@ -2216,9 +2251,6 @@
       <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
@@ -2229,6 +2261,12 @@
       <c r="A14" s="9">
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>90</v>
+      </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
@@ -2295,12 +2333,15 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="36">
+    <row r="21" spans="1:6" ht="54">
       <c r="A21" s="9">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>85</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -2332,6 +2373,9 @@
       <c r="B24" t="s">
         <v>86</v>
       </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
       <c r="D24" t="s">
         <v>20</v>
       </c>
@@ -2355,6 +2399,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -2377,6 +2422,1177 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D622D0A-30D6-4F8F-A6C7-E84A3B56F31E}">
+  <dimension ref="A1:F126"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="7">
+        <v>23</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="7">
+        <v>24</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="7">
+        <v>26</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="9">
+        <v>27</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="9">
+        <v>28</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="9">
+        <v>29</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="9">
+        <v>30</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="7">
+        <v>31</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="9">
+        <v>32</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="9">
+        <v>33</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="9">
+        <v>34</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="9">
+        <v>35</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="7">
+        <v>36</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="7">
+        <v>37</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="7">
+        <v>38</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="9">
+        <v>39</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="9">
+        <v>40</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="7">
+        <v>41</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="7">
+        <v>42</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="7">
+        <v>43</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="9">
+        <v>44</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="9">
+        <v>45</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="9">
+        <v>46</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="7">
+        <v>47</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="7">
+        <v>48</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="7">
+        <v>49</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="9">
+        <v>50</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="9">
+        <v>51</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="9">
+        <v>52</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="9">
+        <v>53</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="9">
+        <v>54</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="7">
+        <v>55</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="7">
+        <v>56</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="7">
+        <v>57</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="9">
+        <v>58</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="9">
+        <v>59</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="9">
+        <v>60</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="9">
+        <v>61</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="9">
+        <v>62</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="7">
+        <v>63</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="7">
+        <v>64</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="9">
+        <v>65</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="9">
+        <v>66</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="9">
+        <v>67</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="9">
+        <v>68</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="7">
+        <v>69</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="7">
+        <v>70</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="9">
+        <v>71</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="9">
+        <v>72</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="9">
+        <v>73</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="9">
+        <v>74</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="9">
+        <v>75</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="7">
+        <v>76</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="9">
+        <v>77</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="9">
+        <v>78</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="9">
+        <v>79</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="9">
+        <v>80</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="9">
+        <v>81</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="9">
+        <v>82</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="9">
+        <v>83</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="9">
+        <v>84</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="7">
+        <v>85</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="9">
+        <v>86</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="9">
+        <v>87</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="9">
+        <v>88</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="7">
+        <v>89</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="9">
+        <v>90</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="9">
+        <v>91</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="9">
+        <v>92</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="9">
+        <v>93</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="7">
+        <v>94</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="9">
+        <v>95</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="9">
+        <v>96</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="9">
+        <v>97</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="7">
+        <v>98</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="7">
+        <v>99</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="9">
+        <v>100</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="9">
+        <v>101</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="9">
+        <v>102</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F103" s="4"/>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="9">
+        <v>103</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F104" s="4"/>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="9">
+        <v>104</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F105" s="4"/>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="9">
+        <v>105</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F106" s="4"/>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="9">
+        <v>106</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F107" s="4"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="9">
+        <v>107</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F108" s="4"/>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="9">
+        <v>108</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F109" s="4"/>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="9">
+        <v>109</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F110" s="4"/>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="9">
+        <v>110</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F111" s="4"/>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="9">
+        <v>111</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F112" s="4"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="9">
+        <v>112</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F113" s="4"/>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="9">
+        <v>113</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F114" s="4"/>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="9">
+        <v>114</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F115" s="4"/>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="9">
+        <v>115</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F116" s="4"/>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" s="9">
+        <v>116</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F117" s="4"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="9">
+        <v>117</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F118" s="4"/>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" s="9">
+        <v>118</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F119" s="4"/>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="9">
+        <v>119</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F120" s="4"/>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="9">
+        <v>120</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F121" s="4"/>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="9">
+        <v>121</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F122" s="4"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="9">
+        <v>122</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F123" s="4"/>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="9">
+        <v>123</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F124" s="4"/>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="9">
+        <v>124</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F125" s="4"/>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="9">
+        <v>125</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{79CD2A85-39AA-449A-8D47-1B3A5BD29F97}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F125 E126</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{92CF31E3-524A-40E2-B6F1-679EB5712B8F}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D125</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64DF754-7974-46D1-A101-C1561FC3B2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8812E01F-9843-4281-A12B-F61AC2CF5B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="107">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -407,6 +407,57 @@
     <t>明るい</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>complimented</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>alphabetically</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>strained</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>harsh</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>puzzle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>waived</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kiosk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほめ</t>
+  </si>
+  <si>
+    <t>アルファベット順</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>痛めた</t>
+  </si>
+  <si>
+    <t>厳しい</t>
+  </si>
+  <si>
+    <t>困惑</t>
+  </si>
+  <si>
+    <t>免除</t>
+  </si>
+  <si>
+    <t>キオスク</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -475,7 +526,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,6 +536,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -501,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -522,6 +579,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2425,6 +2487,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D622D0A-30D6-4F8F-A6C7-E84A3B56F31E}">
   <dimension ref="A1:F126"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="24.69921875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="9"/>
@@ -2529,6 +2594,12 @@
       <c r="A11" s="7">
         <v>10</v>
       </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
       <c r="E11" s="4" t="s">
         <v>5</v>
       </c>
@@ -2557,7 +2628,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14" s="4"/>
     </row>
@@ -2565,6 +2636,12 @@
       <c r="A15" s="7">
         <v>14</v>
       </c>
+      <c r="B15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
       <c r="E15" s="4" t="s">
         <v>5</v>
       </c>
@@ -2574,6 +2651,12 @@
       <c r="A16" s="9">
         <v>15</v>
       </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
       <c r="E16" s="4" t="s">
         <v>5</v>
       </c>
@@ -2655,6 +2738,12 @@
       <c r="A25" s="7">
         <v>24</v>
       </c>
+      <c r="B25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
       <c r="E25" s="4" t="s">
         <v>5</v>
       </c>
@@ -2790,6 +2879,12 @@
       <c r="A40" s="9">
         <v>39</v>
       </c>
+      <c r="B40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" t="s">
+        <v>104</v>
+      </c>
       <c r="E40" s="4" t="s">
         <v>5</v>
       </c>
@@ -2799,6 +2894,12 @@
       <c r="A41" s="9">
         <v>40</v>
       </c>
+      <c r="B41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" t="s">
+        <v>105</v>
+      </c>
       <c r="E41" s="4" t="s">
         <v>5</v>
       </c>
@@ -3016,7 +3117,7 @@
         <v>64</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65" s="4"/>
     </row>
@@ -3060,19 +3161,25 @@
       <c r="A70" s="7">
         <v>69</v>
       </c>
+      <c r="B70" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" t="s">
+        <v>106</v>
+      </c>
       <c r="E70" s="4" t="s">
         <v>5</v>
       </c>
       <c r="F70" s="4"/>
     </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="7">
+    <row r="71" spans="1:6" s="13" customFormat="1">
+      <c r="A71" s="12">
         <v>70</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F71" s="4"/>
+      <c r="E71" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F71" s="14"/>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="9">

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8812E01F-9843-4281-A12B-F61AC2CF5B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3AE11F-FF78-4048-9481-ADE113798C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="109">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -458,6 +458,14 @@
     <t>キオスク</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>engaging</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ethics</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -558,7 +566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -584,6 +592,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3197,7 +3206,6 @@
       <c r="E73" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="9">
@@ -3383,6 +3391,9 @@
       <c r="A94" s="9">
         <v>93</v>
       </c>
+      <c r="B94" s="15" t="s">
+        <v>107</v>
+      </c>
       <c r="E94" s="4" t="s">
         <v>5</v>
       </c>
@@ -3391,6 +3402,9 @@
     <row r="95" spans="1:6">
       <c r="A95" s="7">
         <v>94</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>5</v>
@@ -3685,7 +3699,7 @@
           <x14:formula1>
             <xm:f>list!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:F125 E126</xm:sqref>
+          <xm:sqref>E126 E2:E125 F2:F72 F74:F125</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{92CF31E3-524A-40E2-B6F1-679EB5712B8F}">
           <x14:formula1>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3AE11F-FF78-4048-9481-ADE113798C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B19FC1-20A7-4031-9C49-171943E65891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,9 @@
     <sheet name="toeic12" sheetId="13" r:id="rId12"/>
     <sheet name="toeic13" sheetId="14" r:id="rId13"/>
     <sheet name="toeic14" sheetId="15" r:id="rId14"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId15"/>
+    <sheet name="toeic15" sheetId="16" r:id="rId15"/>
+    <sheet name="Sheet2" sheetId="17" r:id="rId16"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId17"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="109">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -3714,6 +3716,299 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8858198-07BD-4998-B874-DE431301DCEF}">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DFA5843E-A468-4CB1-8499-5EF0E65F7182}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D25</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0125033E-FA49-4B0A-8271-DDFD878F81FD}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F25</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8B8DF8-E33C-4840-A083-5097F3DD09D8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B19FC1-20A7-4031-9C49-171943E65891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A14EC6-4623-4D83-ABF2-ADED7FBB270D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="109">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -3717,7 +3717,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8858198-07BD-4998-B874-DE431301DCEF}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3973,6 +3973,14 @@
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="9">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3984,7 +3992,7 @@
           <x14:formula1>
             <xm:f>list!$B$1:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D25</xm:sqref>
+          <xm:sqref>D2:D26</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0125033E-FA49-4B0A-8271-DDFD878F81FD}">
           <x14:formula1>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A14EC6-4623-4D83-ABF2-ADED7FBB270D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342772A6-C438-45C5-9C8F-8C8214DE35FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="111">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -468,6 +468,16 @@
     <t>ethics</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>breaking up,
+barely</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>別れ、
+ほとんど</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -3758,22 +3768,30 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="54">
       <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="B4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6">
@@ -3860,9 +3878,10 @@
       <c r="A14" s="9">
         <v>13</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6">
@@ -3889,9 +3908,10 @@
       <c r="A17" s="9">
         <v>16</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="4"/>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6">

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342772A6-C438-45C5-9C8F-8C8214DE35FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387ED893-4292-4A88-B256-32A91FA313B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="toeic13" sheetId="14" r:id="rId13"/>
     <sheet name="toeic14" sheetId="15" r:id="rId14"/>
     <sheet name="toeic15" sheetId="16" r:id="rId15"/>
-    <sheet name="Sheet2" sheetId="17" r:id="rId16"/>
+    <sheet name="toeic6" sheetId="17" r:id="rId16"/>
     <sheet name="list" sheetId="2" state="hidden" r:id="rId17"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="111">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -4028,11 +4028,297 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8B8DF8-E33C-4840-A083-5097F3DD09D8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="7">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{39B89406-7112-40DE-A940-3BAB29D9C4F0}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F26</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C32E571D-CDFB-468F-8AFB-7002AF5D03BB}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D26</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387ED893-4292-4A88-B256-32A91FA313B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760CB3D8-5520-4C31-B7EE-337ABFFF41BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="114">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -478,6 +478,18 @@
 ほとんど</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>sparead</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>exploration</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>探査</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -4093,6 +4105,9 @@
       <c r="A6" s="9">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
       <c r="D6" t="s">
         <v>18</v>
       </c>
@@ -4243,9 +4258,10 @@
       <c r="A21" s="9">
         <v>20</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6">
@@ -4261,6 +4277,12 @@
     <row r="23" spans="1:6">
       <c r="A23" s="9">
         <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" t="s">
+        <v>113</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760CB3D8-5520-4C31-B7EE-337ABFFF41BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD94A79-9E40-4044-A006-5701429C3262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,9 @@
     <sheet name="toeic13" sheetId="14" r:id="rId13"/>
     <sheet name="toeic14" sheetId="15" r:id="rId14"/>
     <sheet name="toeic15" sheetId="16" r:id="rId15"/>
-    <sheet name="toeic6" sheetId="17" r:id="rId16"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId17"/>
+    <sheet name="toeic16" sheetId="17" r:id="rId16"/>
+    <sheet name="toeic17" sheetId="18" r:id="rId17"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId18"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="114">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -4345,6 +4346,313 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147FE8DE-20E6-40A1-B65D-5DC90E4CE640}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E5A91CB5-FC11-4E70-8B6F-A37BFBE39679}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{61FE55E7-ACF8-49E4-A091-A4632E6CB3FE}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F29</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD94A79-9E40-4044-A006-5701429C3262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDBE5BE-DFCD-43FF-B201-5890AE4BFC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="120">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -491,12 +491,36 @@
     <t>探査</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>narrowed,
+shortlist</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>vacancies</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cultural</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最終候補リスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠員</t>
+  </si>
+  <si>
+    <t>文化</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,6 +582,12 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Meiryo"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -591,7 +621,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -618,6 +648,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4368,9 +4399,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" ht="54">
       <c r="A2" s="9">
         <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" t="s">
+        <v>117</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -4458,9 +4495,15 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="19.2">
       <c r="A11" s="9">
         <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>118</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
@@ -4512,9 +4555,10 @@
       <c r="A16" s="9">
         <v>15</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6">
@@ -4591,9 +4635,16 @@
       <c r="A24" s="9">
         <v>23</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="B24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6">

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDBE5BE-DFCD-43FF-B201-5890AE4BFC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9359E4-3EE7-4D23-BF1A-8683C2F4F2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,9 @@
     <sheet name="toeic15" sheetId="16" r:id="rId15"/>
     <sheet name="toeic16" sheetId="17" r:id="rId16"/>
     <sheet name="toeic17" sheetId="18" r:id="rId17"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId18"/>
+    <sheet name="Toeic19" sheetId="19" r:id="rId18"/>
+    <sheet name="template" sheetId="20" r:id="rId19"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId20"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="125">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -515,6 +517,26 @@
     <t>文化</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>layover</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乗り継</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>stuck on</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>固執した</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -4704,34 +4726,708 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
-  <dimension ref="A1:B3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5D9A2B-9304-4DD3-B8E3-F1F4D3645E8C}">
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B7" s="3"/>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="E10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="9">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B18" s="3"/>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="9">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="B3" t="s">
+      <c r="B20" s="3"/>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="9">
         <v>21</v>
       </c>
+      <c r="B22" s="3"/>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="9"/>
+      <c r="B27" s="3"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="9"/>
+      <c r="B28" s="3"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="9"/>
+      <c r="B29" s="3"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="9"/>
+      <c r="B30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="9"/>
+      <c r="B31" s="3"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="9"/>
+      <c r="B32" s="3"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="9"/>
+      <c r="B33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="9"/>
+      <c r="B34" s="3"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="9"/>
+      <c r="B35" s="3"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{82F4216D-597A-4495-8A87-ED6BE690FC4F}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F35</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{968F5CA4-48E9-487F-8025-3D530064014E}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D35</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CA1652-010D-4CD5-B2DA-C4FE25700D32}">
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="9">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="9">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="9">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="9">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="9">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="9">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="9">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="9">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="9">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1536C712-7FFF-4E4B-9871-E67CEB5EA6AB}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D35</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB7A5466-31D6-47F4-B37A-875175599D26}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F35</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -5609,6 +6305,38 @@
       </x14:dataValidations>
     </ext>
   </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9359E4-3EE7-4D23-BF1A-8683C2F4F2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE9F679-1821-4A06-AE32-2BDF8FAFF614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="131">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -536,6 +536,29 @@
   <si>
     <t>s</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>samsonite</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bangkok</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>duty-free</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サムソナイト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バンコク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>免税店</t>
   </si>
 </sst>
 </file>
@@ -4758,9 +4781,10 @@
       <c r="C2" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6">
@@ -4845,16 +4869,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="E10" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="36">
       <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" t="s">
+        <v>128</v>
+      </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
@@ -4914,7 +4944,12 @@
       <c r="A16" s="9">
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" t="s">
+        <v>129</v>
+      </c>
       <c r="D16" t="s">
         <v>20</v>
       </c>
@@ -4932,11 +4967,16 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" ht="19.2">
       <c r="A18" s="9">
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>130</v>
+      </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
@@ -4955,7 +4995,7 @@
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="9">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
       <c r="B20" s="3"/>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE9F679-1821-4A06-AE32-2BDF8FAFF614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2395DBFF-C32A-4E72-82DA-7FAE9FBA4187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,9 @@
     <sheet name="toeic16" sheetId="17" r:id="rId16"/>
     <sheet name="toeic17" sheetId="18" r:id="rId17"/>
     <sheet name="Toeic19" sheetId="19" r:id="rId18"/>
-    <sheet name="template" sheetId="20" r:id="rId19"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId20"/>
+    <sheet name="Toeic20" sheetId="21" r:id="rId19"/>
+    <sheet name="template" sheetId="20" r:id="rId20"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId21"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="143">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -560,12 +561,77 @@
   <si>
     <t>免税店</t>
   </si>
+  <si>
+    <t>salmon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dressing,
+balsamic vinaigrette</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>signature</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>still  water</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>deserted</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>vegetation
+risotto</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サーモン</t>
+  </si>
+  <si>
+    <t>ドレッシング,
+バルサミコビネグレット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>署名</t>
+  </si>
+  <si>
+    <t>炭酸なし</t>
+    <rPh sb="0" eb="2">
+      <t>タンサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>寂れた</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">植、
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杂炊</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -632,6 +698,13 @@
       <color rgb="FF000000"/>
       <name val="Meiryo"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -5153,7 +5226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CA1652-010D-4CD5-B2DA-C4FE25700D32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F84ED774-1DA0-49B3-90C9-AF54E975FFA2}">
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
@@ -5180,6 +5253,9 @@
         <v>1</v>
       </c>
       <c r="B2" s="3"/>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
@@ -5188,6 +5264,9 @@
         <v>2</v>
       </c>
       <c r="B3" s="3"/>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
@@ -5196,6 +5275,9 @@
         <v>3</v>
       </c>
       <c r="B4" s="3"/>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
@@ -5204,6 +5286,9 @@
         <v>4</v>
       </c>
       <c r="B5" s="3"/>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
@@ -5212,6 +5297,9 @@
         <v>5</v>
       </c>
       <c r="B6" s="3"/>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
@@ -5220,14 +5308,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="3"/>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" ht="19.2">
       <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
@@ -5236,6 +5335,9 @@
         <v>8</v>
       </c>
       <c r="B9" s="3"/>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
@@ -5244,6 +5346,9 @@
         <v>9</v>
       </c>
       <c r="B10" s="3"/>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
@@ -5252,6 +5357,9 @@
         <v>10</v>
       </c>
       <c r="B11" s="3"/>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
@@ -5260,15 +5368,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="3"/>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" ht="90">
       <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="E13" s="4"/>
+      <c r="B13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6">
@@ -5276,6 +5394,9 @@
         <v>13</v>
       </c>
       <c r="B14" s="3"/>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
@@ -5284,6 +5405,9 @@
         <v>14</v>
       </c>
       <c r="B15" s="3"/>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
@@ -5292,6 +5416,9 @@
         <v>15</v>
       </c>
       <c r="B16" s="3"/>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
@@ -5300,14 +5427,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="3"/>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" ht="19.2">
       <c r="A18" s="9">
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
@@ -5316,6 +5454,9 @@
         <v>18</v>
       </c>
       <c r="B19" s="3"/>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
     </row>
@@ -5324,6 +5465,9 @@
         <v>19</v>
       </c>
       <c r="B20" s="3"/>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
@@ -5332,6 +5476,9 @@
         <v>20</v>
       </c>
       <c r="B21" s="3"/>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
@@ -5340,14 +5487,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="3"/>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" ht="36">
       <c r="A23" s="9">
         <v>22</v>
       </c>
-      <c r="B23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
@@ -5355,15 +5513,31 @@
       <c r="A24" s="9">
         <v>23</v>
       </c>
-      <c r="B24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" ht="54">
       <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
@@ -5372,6 +5546,9 @@
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
@@ -5453,17 +5630,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1536C712-7FFF-4E4B-9871-E67CEB5EA6AB}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4E95BA1B-A01B-4094-A3FE-2977EE59B3D7}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F35</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8962506F-AA3A-418E-BAB3-A5698B264473}">
           <x14:formula1>
             <xm:f>list!$B$1:$B$3</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D35</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB7A5466-31D6-47F4-B37A-875175599D26}">
-          <x14:formula1>
-            <xm:f>list!$A$1:$A$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:F35</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6349,6 +6526,325 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CA1652-010D-4CD5-B2DA-C4FE25700D32}">
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="9">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="9">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="9">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="9">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="9">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="9">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="9">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="9">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="9">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1536C712-7FFF-4E4B-9871-E67CEB5EA6AB}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D35</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB7A5466-31D6-47F4-B37A-875175599D26}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F35</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2395DBFF-C32A-4E72-82DA-7FAE9FBA4187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6679C1-2036-46D8-8008-E52B6C1D8A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8145" yWindow="-15585" windowWidth="17280" windowHeight="11385" firstSheet="12" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="146">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -594,9 +594,6 @@
     <t>ドレッシング,
 バルサミコビネグレット</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>署名</t>
   </si>
   <si>
     <t>炭酸なし</t>
@@ -624,6 +621,25 @@
       </rPr>
       <t>杂炊</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>care for</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>看板</t>
+    <rPh sb="0" eb="2">
+      <t>カンバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hallway</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>廊下</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -739,7 +755,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -767,6 +783,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5384,9 +5403,10 @@
       <c r="C13" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6">
@@ -5415,7 +5435,9 @@
       <c r="A16" s="9">
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="17" t="s">
+        <v>142</v>
+      </c>
       <c r="D16" t="s">
         <v>18</v>
       </c>
@@ -5433,15 +5455,15 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="19.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="9">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="16" t="s">
-        <v>139</v>
+      <c r="C18" t="s">
+        <v>143</v>
       </c>
       <c r="D18" t="s">
         <v>16</v>
@@ -5449,11 +5471,12 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" ht="19.2">
       <c r="A19" s="9">
         <v>18</v>
       </c>
       <c r="B19" s="3"/>
+      <c r="C19" s="16"/>
       <c r="D19" t="s">
         <v>20</v>
       </c>
@@ -5464,7 +5487,12 @@
       <c r="A20" s="9">
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" t="s">
+        <v>145</v>
+      </c>
       <c r="D20" t="s">
         <v>16</v>
       </c>
@@ -5501,7 +5529,7 @@
         <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
@@ -5517,7 +5545,7 @@
         <v>135</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -5533,7 +5561,7 @@
         <v>136</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6679C1-2036-46D8-8008-E52B6C1D8A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2C4B8F-233D-482E-8A7C-C722B2BA513C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8145" yWindow="-15585" windowWidth="17280" windowHeight="11385" firstSheet="12" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="14" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -32,8 +32,9 @@
     <sheet name="toeic17" sheetId="18" r:id="rId17"/>
     <sheet name="Toeic19" sheetId="19" r:id="rId18"/>
     <sheet name="Toeic20" sheetId="21" r:id="rId19"/>
-    <sheet name="template" sheetId="20" r:id="rId20"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId21"/>
+    <sheet name="toeic21" sheetId="22" r:id="rId20"/>
+    <sheet name="template" sheetId="20" r:id="rId21"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId22"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="146">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -723,7 +724,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -742,6 +743,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -755,7 +762,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -786,6 +793,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6554,6 +6562,1084 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2066A85F-5163-46AB-9699-869EDBF5BEEF}">
+  <dimension ref="A1:F110"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="9"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="E8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="E16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="E17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="9">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="9">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="9">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="9">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="9">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="9">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="9">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="9">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="18">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="9">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="D36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="9">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="9">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="9">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="18">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="E40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="9">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="E41" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="9">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="9">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="D43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="9">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="9">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="9">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="D46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="9">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="D47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="9">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="D48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="9">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="E49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="9">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="9">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="9">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="9">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="9">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="9">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3"/>
+      <c r="D55" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="9">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="9">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="9">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="9">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="9">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="9">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="9">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="9">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="9">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="9">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="9">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="9">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="9">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="9">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="9">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="9">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="9">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="9">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="9">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="9">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="9">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="9">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="9">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="9">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="9">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="9">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="9">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="9">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="9">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="9">
+        <v>84</v>
+      </c>
+      <c r="B85" s="3"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="9">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="9">
+        <v>86</v>
+      </c>
+      <c r="B87" s="3"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="9">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="9">
+        <v>88</v>
+      </c>
+      <c r="B89" s="3"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="9">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="9">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="9">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="9">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="9">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="9">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="9">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="9">
+        <v>96</v>
+      </c>
+      <c r="B97" s="3"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="9">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="9">
+        <v>98</v>
+      </c>
+      <c r="B99" s="3"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="9">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="9">
+        <v>100</v>
+      </c>
+      <c r="B101" s="3"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="9">
+        <v>101</v>
+      </c>
+      <c r="B102" s="3"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="9">
+        <v>102</v>
+      </c>
+      <c r="B103" s="3"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="9">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="9">
+        <v>104</v>
+      </c>
+      <c r="B105" s="3"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="9">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="9">
+        <v>106</v>
+      </c>
+      <c r="B107" s="3"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="9">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="9">
+        <v>108</v>
+      </c>
+      <c r="B109" s="3"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="9">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{470C677D-769B-40B4-AB50-69AB8BCC3228}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F110</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F4556D43-8996-463E-8D6F-372D06AB7E41}">
+          <x14:formula1>
+            <xm:f>list!$B$1:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D110</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CA1652-010D-4CD5-B2DA-C4FE25700D32}">
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -6872,7 +7958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2C4B8F-233D-482E-8A7C-C722B2BA513C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3229AAA3-94EA-4B4E-B8CD-88B488BFA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="14" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="146">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -6563,7 +6563,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2066A85F-5163-46AB-9699-869EDBF5BEEF}">
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7188,6 +7188,9 @@
         <v>56</v>
       </c>
       <c r="B57" s="3"/>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
     </row>
@@ -7196,6 +7199,9 @@
         <v>57</v>
       </c>
       <c r="B58" s="3"/>
+      <c r="D58" t="s">
+        <v>16</v>
+      </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
     </row>
@@ -7204,6 +7210,9 @@
         <v>58</v>
       </c>
       <c r="B59" s="3"/>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
     </row>
@@ -7212,6 +7221,9 @@
         <v>59</v>
       </c>
       <c r="B60" s="3"/>
+      <c r="D60" t="s">
+        <v>18</v>
+      </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
     </row>
@@ -7220,6 +7232,9 @@
         <v>60</v>
       </c>
       <c r="B61" s="3"/>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
     </row>
@@ -7228,6 +7243,9 @@
         <v>61</v>
       </c>
       <c r="B62" s="3"/>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
     </row>
@@ -7236,6 +7254,9 @@
         <v>62</v>
       </c>
       <c r="B63" s="3"/>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
     </row>
@@ -7244,6 +7265,9 @@
         <v>63</v>
       </c>
       <c r="B64" s="3"/>
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
     </row>
@@ -7252,6 +7276,9 @@
         <v>64</v>
       </c>
       <c r="B65" s="3"/>
+      <c r="D65" t="s">
+        <v>16</v>
+      </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
     </row>
@@ -7260,6 +7287,9 @@
         <v>65</v>
       </c>
       <c r="B66" s="3"/>
+      <c r="D66" t="s">
+        <v>16</v>
+      </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
     </row>
@@ -7268,6 +7298,9 @@
         <v>66</v>
       </c>
       <c r="B67" s="3"/>
+      <c r="D67" t="s">
+        <v>16</v>
+      </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
     </row>
@@ -7276,6 +7309,9 @@
         <v>67</v>
       </c>
       <c r="B68" s="3"/>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
     </row>
@@ -7284,6 +7320,9 @@
         <v>68</v>
       </c>
       <c r="B69" s="3"/>
+      <c r="D69" t="s">
+        <v>20</v>
+      </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
     </row>
@@ -7292,6 +7331,9 @@
         <v>69</v>
       </c>
       <c r="B70" s="3"/>
+      <c r="D70" t="s">
+        <v>20</v>
+      </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
     </row>
@@ -7300,6 +7342,9 @@
         <v>70</v>
       </c>
       <c r="B71" s="3"/>
+      <c r="D71" t="s">
+        <v>16</v>
+      </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
     </row>
@@ -7308,6 +7353,9 @@
         <v>71</v>
       </c>
       <c r="B72" s="3"/>
+      <c r="D72" t="s">
+        <v>16</v>
+      </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
     </row>
@@ -7316,6 +7364,9 @@
         <v>72</v>
       </c>
       <c r="B73" s="3"/>
+      <c r="D73" t="s">
+        <v>18</v>
+      </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
     </row>
@@ -7324,6 +7375,9 @@
         <v>73</v>
       </c>
       <c r="B74" s="3"/>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
     </row>
@@ -7332,7 +7386,9 @@
         <v>74</v>
       </c>
       <c r="B75" s="3"/>
-      <c r="E75" s="4"/>
+      <c r="E75" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F75" s="4"/>
     </row>
     <row r="76" spans="1:6">
@@ -7340,6 +7396,9 @@
         <v>75</v>
       </c>
       <c r="B76" s="3"/>
+      <c r="D76" t="s">
+        <v>18</v>
+      </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
     </row>
@@ -7348,6 +7407,9 @@
         <v>76</v>
       </c>
       <c r="B77" s="3"/>
+      <c r="D77" t="s">
+        <v>16</v>
+      </c>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
     </row>
@@ -7356,6 +7418,9 @@
         <v>77</v>
       </c>
       <c r="B78" s="3"/>
+      <c r="D78" t="s">
+        <v>16</v>
+      </c>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
     </row>
@@ -7364,6 +7429,9 @@
         <v>78</v>
       </c>
       <c r="B79" s="3"/>
+      <c r="D79" t="s">
+        <v>20</v>
+      </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
     </row>
@@ -7372,6 +7440,9 @@
         <v>79</v>
       </c>
       <c r="B80" s="3"/>
+      <c r="D80" t="s">
+        <v>16</v>
+      </c>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
     </row>
@@ -7380,6 +7451,9 @@
         <v>80</v>
       </c>
       <c r="B81" s="3"/>
+      <c r="D81" t="s">
+        <v>20</v>
+      </c>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
     </row>
@@ -7388,6 +7462,9 @@
         <v>81</v>
       </c>
       <c r="B82" s="3"/>
+      <c r="D82" t="s">
+        <v>18</v>
+      </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
     </row>
@@ -7396,6 +7473,9 @@
         <v>82</v>
       </c>
       <c r="B83" s="3"/>
+      <c r="D83" t="s">
+        <v>18</v>
+      </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
     </row>
@@ -7404,6 +7484,9 @@
         <v>83</v>
       </c>
       <c r="B84" s="3"/>
+      <c r="D84" t="s">
+        <v>20</v>
+      </c>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
     </row>
@@ -7412,7 +7495,9 @@
         <v>84</v>
       </c>
       <c r="B85" s="3"/>
-      <c r="E85" s="4"/>
+      <c r="E85" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6">
@@ -7420,6 +7505,9 @@
         <v>85</v>
       </c>
       <c r="B86" s="3"/>
+      <c r="D86" t="s">
+        <v>16</v>
+      </c>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
     </row>
@@ -7428,6 +7516,9 @@
         <v>86</v>
       </c>
       <c r="B87" s="3"/>
+      <c r="D87" t="s">
+        <v>20</v>
+      </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
     </row>
@@ -7436,6 +7527,9 @@
         <v>87</v>
       </c>
       <c r="B88" s="3"/>
+      <c r="D88" t="s">
+        <v>20</v>
+      </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
     </row>
@@ -7444,6 +7538,9 @@
         <v>88</v>
       </c>
       <c r="B89" s="3"/>
+      <c r="D89" t="s">
+        <v>16</v>
+      </c>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
     </row>
@@ -7452,6 +7549,9 @@
         <v>89</v>
       </c>
       <c r="B90" s="3"/>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
     </row>
@@ -7460,7 +7560,9 @@
         <v>90</v>
       </c>
       <c r="B91" s="3"/>
-      <c r="E91" s="4"/>
+      <c r="E91" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6">
@@ -7468,6 +7570,9 @@
         <v>91</v>
       </c>
       <c r="B92" s="3"/>
+      <c r="D92" t="s">
+        <v>16</v>
+      </c>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
     </row>
@@ -7476,6 +7581,9 @@
         <v>92</v>
       </c>
       <c r="B93" s="3"/>
+      <c r="D93" t="s">
+        <v>16</v>
+      </c>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
     </row>
@@ -7484,6 +7592,9 @@
         <v>93</v>
       </c>
       <c r="B94" s="3"/>
+      <c r="D94" t="s">
+        <v>18</v>
+      </c>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
     </row>
@@ -7492,6 +7603,9 @@
         <v>94</v>
       </c>
       <c r="B95" s="3"/>
+      <c r="D95" t="s">
+        <v>20</v>
+      </c>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
     </row>
@@ -7500,6 +7614,9 @@
         <v>95</v>
       </c>
       <c r="B96" s="3"/>
+      <c r="D96" t="s">
+        <v>16</v>
+      </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
     </row>
@@ -7508,6 +7625,9 @@
         <v>96</v>
       </c>
       <c r="B97" s="3"/>
+      <c r="D97" t="s">
+        <v>16</v>
+      </c>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
     </row>
@@ -7516,6 +7636,9 @@
         <v>97</v>
       </c>
       <c r="B98" s="3"/>
+      <c r="D98" t="s">
+        <v>20</v>
+      </c>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
     </row>
@@ -7524,6 +7647,9 @@
         <v>98</v>
       </c>
       <c r="B99" s="3"/>
+      <c r="D99" t="s">
+        <v>18</v>
+      </c>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
     </row>
@@ -7532,6 +7658,9 @@
         <v>99</v>
       </c>
       <c r="B100" s="3"/>
+      <c r="D100" t="s">
+        <v>20</v>
+      </c>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
     </row>
@@ -7540,7 +7669,9 @@
         <v>100</v>
       </c>
       <c r="B101" s="3"/>
-      <c r="E101" s="4"/>
+      <c r="E101" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F101" s="4"/>
     </row>
     <row r="102" spans="1:6">
@@ -7548,6 +7679,9 @@
         <v>101</v>
       </c>
       <c r="B102" s="3"/>
+      <c r="D102" t="s">
+        <v>20</v>
+      </c>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
     </row>
@@ -7556,6 +7690,9 @@
         <v>102</v>
       </c>
       <c r="B103" s="3"/>
+      <c r="D103" t="s">
+        <v>16</v>
+      </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
     </row>
@@ -7564,6 +7701,9 @@
         <v>103</v>
       </c>
       <c r="B104" s="3"/>
+      <c r="D104" t="s">
+        <v>16</v>
+      </c>
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
     </row>
@@ -7572,6 +7712,9 @@
         <v>104</v>
       </c>
       <c r="B105" s="3"/>
+      <c r="D105" t="s">
+        <v>16</v>
+      </c>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
     </row>
@@ -7580,6 +7723,9 @@
         <v>105</v>
       </c>
       <c r="B106" s="3"/>
+      <c r="D106" t="s">
+        <v>20</v>
+      </c>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
     </row>
@@ -7588,6 +7734,9 @@
         <v>106</v>
       </c>
       <c r="B107" s="3"/>
+      <c r="D107" t="s">
+        <v>16</v>
+      </c>
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
     </row>
@@ -7596,6 +7745,9 @@
         <v>107</v>
       </c>
       <c r="B108" s="3"/>
+      <c r="D108" t="s">
+        <v>18</v>
+      </c>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
     </row>
@@ -7604,6 +7756,9 @@
         <v>108</v>
       </c>
       <c r="B109" s="3"/>
+      <c r="D109" t="s">
+        <v>20</v>
+      </c>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
     </row>
@@ -7612,8 +7767,20 @@
         <v>109</v>
       </c>
       <c r="B110" s="3"/>
+      <c r="D110" t="s">
+        <v>20</v>
+      </c>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="9">
+        <v>110</v>
+      </c>
+      <c r="B111" s="3"/>
+      <c r="D111" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -7631,7 +7798,7 @@
           <x14:formula1>
             <xm:f>list!$B$1:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D110</xm:sqref>
+          <xm:sqref>D2:D111</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3229AAA3-94EA-4B4E-B8CD-88B488BFA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DAE54D-42E8-4139-96EC-10915F82EC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="152">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -641,6 +641,32 @@
   </si>
   <si>
     <t>廊下</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>wing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>council</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>placeholder</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>棟</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>評議会</t>
+  </si>
+  <si>
+    <t>仮</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -762,7 +788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -794,6 +820,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6645,7 +6675,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -6655,9 +6685,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="E8" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6">
@@ -6742,9 +6773,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="E16" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6">
@@ -6752,9 +6784,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3"/>
-      <c r="E17" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="4"/>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6">
@@ -6772,7 +6805,12 @@
       <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" t="s">
+        <v>149</v>
+      </c>
       <c r="D19" t="s">
         <v>16</v>
       </c>
@@ -6999,14 +7037,20 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" ht="19.2">
       <c r="A40" s="18">
         <v>39</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="E40" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="B40" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="4"/>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6">
@@ -7014,9 +7058,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="3"/>
-      <c r="E41" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="4"/>
       <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6">
@@ -7101,9 +7146,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="3"/>
-      <c r="E49" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D49" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="4"/>
       <c r="F49" s="4"/>
     </row>
     <row r="50" spans="1:6">
@@ -7220,7 +7266,12 @@
       <c r="A60" s="9">
         <v>59</v>
       </c>
-      <c r="B60" s="3"/>
+      <c r="B60" t="s">
+        <v>148</v>
+      </c>
+      <c r="C60" t="s">
+        <v>151</v>
+      </c>
       <c r="D60" t="s">
         <v>18</v>
       </c>
@@ -7238,16 +7289,16 @@
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
     </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="9">
+    <row r="62" spans="1:6" s="13" customFormat="1">
+      <c r="A62" s="19">
         <v>61</v>
       </c>
-      <c r="B62" s="3"/>
-      <c r="D62" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
+      <c r="B62" s="20"/>
+      <c r="D62" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="9">

--- a/Toeic/part2/ReviewWords.xlsx
+++ b/Toeic/part2/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DAE54D-42E8-4139-96EC-10915F82EC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8137B962-44D0-455E-A80C-3F8BF6261DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
@@ -7437,9 +7437,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="3"/>
-      <c r="E75" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D75" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" s="4"/>
       <c r="F75" s="4"/>
     </row>
     <row r="76" spans="1:6">
@@ -7546,9 +7547,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="3"/>
-      <c r="E85" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D85" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" s="4"/>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6">
@@ -7611,9 +7613,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="3"/>
-      <c r="E91" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" s="4"/>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6">
@@ -7720,9 +7723,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="3"/>
-      <c r="E101" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D101" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101" s="4"/>
       <c r="F101" s="4"/>
     </row>
     <row r="102" spans="1:6">
